--- a/artfynd/A 43190-2022 artfynd.xlsx
+++ b/artfynd/A 43190-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43190-2022 artfynd.xlsx
+++ b/artfynd/A 43190-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104478306</v>
+        <v>104471090</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Patronbodarna, Jmt</t>
+          <t>Patronbodarna Ö , Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477851.586089253</v>
+        <v>477867</v>
       </c>
       <c r="R2" t="n">
-        <v>7019219.742936474</v>
+        <v>7019418</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +744,9 @@
           <t>2022-11-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-11-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,12 +761,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall, Kristofer Holmsten</t>
+          <t>Johan Råghall, Benny Öwre, Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -790,12 +776,7 @@
         <v>104470803</v>
       </c>
       <c r="B3" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -828,10 +809,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477819.8368991898</v>
+        <v>477820</v>
       </c>
       <c r="R3" t="n">
-        <v>7019252.342039842</v>
+        <v>7019253</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -861,19 +842,9 @@
           <t>2022-11-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-11-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,37 +871,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104470840</v>
+        <v>104470837</v>
       </c>
       <c r="B4" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -941,10 +907,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477832.3488586425</v>
+        <v>477833</v>
       </c>
       <c r="R4" t="n">
-        <v>7019303.523756493</v>
+        <v>7019304</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,19 +940,9 @@
           <t>2022-11-04</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-11-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,53 +969,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104478314</v>
+        <v>104471160</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Patronbodarna, Jmt</t>
+          <t>Patronbodarna Ö , Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477837.948637802</v>
+        <v>477867</v>
       </c>
       <c r="R5" t="n">
-        <v>7019266.608238539</v>
+        <v>7019446</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,19 +1038,9 @@
           <t>2022-11-04</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-11-04</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,27 +1055,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall, Kristofer Holmsten</t>
+          <t>Johan Råghall, Benny Öwre, Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104478304</v>
+        <v>104478306</v>
       </c>
       <c r="B6" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1141,21 +1078,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1165,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477831.6783880585</v>
+        <v>477851</v>
       </c>
       <c r="R6" t="n">
-        <v>7019271.598396252</v>
+        <v>7019220</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,19 +1135,9 @@
           <t>2022-11-04</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-11-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,15 +1164,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104471160</v>
+        <v>104478308</v>
       </c>
       <c r="B7" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,20 +1193,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Patronbodarna Ö , Jmt</t>
+          <t>Patronbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477866.6529919329</v>
+        <v>477865</v>
       </c>
       <c r="R7" t="n">
-        <v>7019445.844157451</v>
+        <v>7019213</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1311,19 +1232,9 @@
           <t>2022-11-04</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-11-04</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1338,49 +1249,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Johan Råghall, Benny Öwre, Kristofer Holmsten</t>
+          <t>Benny Öwre, Johan Råghall, Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104470837</v>
+        <v>104470840</v>
       </c>
       <c r="B8" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477832.3488586425</v>
+        <v>477833</v>
       </c>
       <c r="R8" t="n">
-        <v>7019303.523756493</v>
+        <v>7019304</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1424,19 +1330,9 @@
           <t>2022-11-04</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-11-04</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,37 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104478313</v>
+        <v>104478304</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1503,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477862.8661966417</v>
+        <v>477832</v>
       </c>
       <c r="R9" t="n">
-        <v>7019353.681249088</v>
+        <v>7019271</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,19 +1427,9 @@
           <t>2022-11-04</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-11-04</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,54 +1456,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104471090</v>
+        <v>104478313</v>
       </c>
       <c r="B10" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Patronbodarna Ö , Jmt</t>
+          <t>Patronbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477866.9113252966</v>
+        <v>477863</v>
       </c>
       <c r="R10" t="n">
-        <v>7019417.961111057</v>
+        <v>7019354</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1649,19 +1524,9 @@
           <t>2022-11-04</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-11-04</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1676,49 +1541,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Johan Råghall, Benny Öwre, Kristofer Holmsten</t>
+          <t>Benny Öwre, Johan Råghall, Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104478308</v>
+        <v>104478314</v>
       </c>
       <c r="B11" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1728,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477865.499504296</v>
+        <v>477838</v>
       </c>
       <c r="R11" t="n">
-        <v>7019212.901194925</v>
+        <v>7019266</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1761,19 +1621,9 @@
           <t>2022-11-04</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-11-04</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 43190-2022 artfynd.xlsx
+++ b/artfynd/A 43190-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104471090</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104470803</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -966,6 +981,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104470837</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104471160</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104478306</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104478308</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104470840</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104478304</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1550,6 +1595,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104478313</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1647,8 +1697,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104478314</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>